--- a/summary/yes/exposures_meta_analysis_prostate_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_prostate_cancer_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A2" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,12 +524,12 @@
       <c r="E2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
       <c r="H2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>204</v>
       </c>
@@ -540,10 +538,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>natto</t>
-        </is>
+      <c r="A3" t="str">
+        <v>natto</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -557,12 +553,12 @@
       <c r="E3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>280</v>
       </c>
@@ -571,10 +567,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>papaya</t>
-        </is>
+      <c r="A4" t="str">
+        <v>papaya</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -588,12 +582,12 @@
       <c r="E4" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>105</v>
       </c>
@@ -602,10 +596,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>early_time_restricted_eating</t>
-        </is>
+      <c r="A5" t="str">
+        <v>early_time_restricted_eating</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -619,12 +611,12 @@
       <c r="E5" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>1455</v>
       </c>
@@ -633,10 +625,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>soy</t>
-        </is>
+      <c r="A6" t="str">
+        <v>soy</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>8</v>
@@ -657,7 +647,7 @@
         <v>2.09</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>78.9</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0.1010785350953814</v>
@@ -670,10 +660,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A7" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>7</v>
@@ -707,10 +695,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A8" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>3</v>
@@ -731,7 +717,7 @@
         <v>206.11</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>74.9</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0.1151715356999109</v>
@@ -739,13 +725,11 @@
       <c r="J8" s="2" t="n">
         <v>101084</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>low_fat_diet</t>
-        </is>
+      <c r="A9" t="str">
+        <v>low_fat_diet</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -759,12 +743,12 @@
       <c r="E9" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="2" t="n">
         <v>1170</v>
       </c>
@@ -773,10 +757,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A10" t="str">
+        <v>lutein</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2</v>
@@ -790,12 +772,12 @@
       <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="2" t="n">
         <v>1623</v>
       </c>
@@ -804,10 +786,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>vitamin_k</t>
-        </is>
+      <c r="A11" t="str">
+        <v>vitamin_k</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -821,12 +801,12 @@
       <c r="E11" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
       <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="2" t="n">
         <v>11319</v>
       </c>
@@ -835,10 +815,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>vitamin_k2</t>
-        </is>
+      <c r="A12" t="str">
+        <v>vitamin_k2</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -852,12 +830,12 @@
       <c r="E12" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
       <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="2" t="n">
         <v>11319</v>
       </c>
@@ -866,10 +844,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A13" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -883,12 +859,12 @@
       <c r="E13" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="2" t="n">
         <v>971</v>
       </c>
@@ -897,10 +873,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>vegan_diet</t>
-        </is>
+      <c r="A14" t="str">
+        <v>vegan_diet</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -914,12 +888,12 @@
       <c r="E14" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="2" t="n">
         <v>26346</v>
       </c>
@@ -928,16 +902,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>garlic</t>
-        </is>
+      <c r="A15" t="str">
+        <v>garlic</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.42</v>
@@ -965,10 +937,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>vegetarian_diet</t>
-        </is>
+      <c r="A16" t="str">
+        <v>vegetarian_diet</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -977,17 +947,17 @@
         <v>0.7</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.56</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="inlineStr"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="2" t="n">
         <v>217937</v>
       </c>
@@ -996,10 +966,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A17" t="str">
+        <v>tomato</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>11</v>
@@ -1020,10 +988,10 @@
         <v>1.16</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>78.1</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>2.045420729252852e-05</v>
+        <v>0.00002045420729252852</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1057923</v>
@@ -1033,10 +1001,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A18" t="str">
+        <v>tea</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>10</v>
@@ -1057,7 +1023,7 @@
         <v>1.27</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>84.9</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0.04996208468350858</v>
@@ -1070,10 +1036,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A19" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1087,12 +1051,12 @@
       <c r="E19" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="2" t="n">
         <v>652</v>
       </c>
@@ -1101,10 +1065,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A20" t="str">
+        <v>potassium</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1118,12 +1080,12 @@
       <c r="E20" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>656</v>
       </c>
@@ -1132,10 +1094,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>genistein</t>
-        </is>
+      <c r="A21" t="str">
+        <v>genistein</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>3</v>
@@ -1169,10 +1129,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>iodine</t>
-        </is>
+      <c r="A22" t="str">
+        <v>iodine</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1186,12 +1144,12 @@
       <c r="E22" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
       <c r="H22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="2" t="n">
         <v>656</v>
       </c>
@@ -1200,10 +1158,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A23" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>10</v>
@@ -1232,13 +1188,11 @@
       <c r="J23" s="2" t="n">
         <v>94949</v>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time_restricted_eating</t>
-        </is>
+      <c r="A24" t="str">
+        <v>time_restricted_eating</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1252,12 +1206,12 @@
       <c r="E24" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>1455</v>
       </c>
@@ -1266,10 +1220,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A25" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1283,12 +1235,12 @@
       <c r="E25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="2" t="n">
         <v>2745</v>
       </c>
@@ -1297,10 +1249,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>omega_6_fatty_acids</t>
-        </is>
+      <c r="A26" t="str">
+        <v>omega_6_fatty_acids</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1314,12 +1264,12 @@
       <c r="E26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
       <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="2" t="n">
         <v>2745</v>
       </c>
@@ -1328,10 +1278,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>mushrooms</t>
-        </is>
+      <c r="A27" t="str">
+        <v>mushrooms</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1345,12 +1293,12 @@
       <c r="E27" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>36499</v>
       </c>
@@ -1359,10 +1307,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A28" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>10</v>
@@ -1396,10 +1342,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A29" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>13</v>
@@ -1433,10 +1377,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A30" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>5</v>
@@ -1465,13 +1407,11 @@
       <c r="J30" s="2" t="n">
         <v>131386</v>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>legumes</t>
-        </is>
+      <c r="A31" t="str">
+        <v>legumes</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>8</v>
@@ -1480,7 +1420,7 @@
         <v>0.89</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0.97</v>
@@ -1505,10 +1445,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>soluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A32" t="str">
+        <v>soluble_dietary_fiber_intake</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>3</v>
@@ -1542,10 +1480,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A33" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>3</v>
@@ -1579,10 +1515,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>plant_based_diet</t>
-        </is>
+      <c r="A34" t="str">
+        <v>plant_based_diet</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>2</v>
@@ -1596,12 +1530,12 @@
       <c r="E34" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
+      <c r="I34" s="5"/>
       <c r="J34" s="2" t="n">
         <v>211318</v>
       </c>
@@ -1610,10 +1544,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>caffeine</t>
-        </is>
+      <c r="A35" t="str">
+        <v>caffeine</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -1627,12 +1559,12 @@
       <c r="E35" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>46667</v>
       </c>
@@ -1641,10 +1573,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ginseng</t>
-        </is>
+      <c r="A36" t="str">
+        <v>ginseng</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1658,12 +1588,12 @@
       <c r="E36" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>35239</v>
       </c>
@@ -1672,10 +1602,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A37" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>7</v>
@@ -1709,10 +1637,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>dash_diet</t>
-        </is>
+      <c r="A38" t="str">
+        <v>dash_diet</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>2</v>
@@ -1726,22 +1652,20 @@
       <c r="E38" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
       <c r="H38" s="4" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="I38" s="5" t="inlineStr"/>
+        <v>73.9</v>
+      </c>
+      <c r="I38" s="5"/>
       <c r="J38" s="2" t="n">
         <v>152714</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ginkgo_biloba</t>
-        </is>
+      <c r="A39" t="str">
+        <v>ginkgo_biloba</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
@@ -1755,12 +1679,12 @@
       <c r="E39" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="I39" s="5" t="inlineStr"/>
+      <c r="I39" s="5"/>
       <c r="J39" s="2" t="n">
         <v>38308</v>
       </c>
@@ -1769,16 +1693,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>coenzyme_q10</t>
-        </is>
+      <c r="A40" t="str">
+        <v>coenzyme_q10</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0.76</v>
@@ -1786,12 +1708,12 @@
       <c r="E40" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="I40" s="5"/>
       <c r="J40" s="2" t="n">
         <v>35239</v>
       </c>
@@ -1800,10 +1722,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>eicosapentaenoic_acid</t>
-        </is>
+      <c r="A41" t="str">
+        <v>eicosapentaenoic_acid</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>2</v>
@@ -1817,12 +1737,12 @@
       <c r="E41" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
       <c r="H41" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
+      <c r="I41" s="5"/>
       <c r="J41" s="2" t="n">
         <v>430507</v>
       </c>
@@ -1831,10 +1751,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A42" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>13</v>
@@ -1855,7 +1773,7 @@
         <v>1.34</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>73.40000000000001</v>
+        <v>73.4</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>0.116278835132563</v>
@@ -1868,10 +1786,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fish_oil</t>
-        </is>
+      <c r="A43" t="str">
+        <v>fish_oil</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1885,12 +1801,12 @@
       <c r="E43" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
         <v>35239</v>
       </c>
@@ -1899,10 +1815,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>plant_protein_intake</t>
-        </is>
+      <c r="A44" t="str">
+        <v>plant_protein_intake</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1916,12 +1830,12 @@
       <c r="E44" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
       <c r="H44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="5" t="inlineStr"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="2" t="n">
         <v>150671</v>
       </c>
@@ -1930,10 +1844,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A45" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -1942,17 +1854,17 @@
         <v>0.99</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
       <c r="H45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="5" t="inlineStr"/>
+      <c r="I45" s="5"/>
       <c r="J45" s="2" t="n">
         <v>159482</v>
       </c>
@@ -1961,10 +1873,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A46" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>2</v>
@@ -1978,12 +1888,12 @@
       <c r="E46" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="5" t="inlineStr"/>
+      <c r="I46" s="5"/>
       <c r="J46" s="2" t="n">
         <v>109557</v>
       </c>
@@ -1992,10 +1902,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A47" t="str">
+        <v>eggs</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>3</v>
@@ -2010,7 +1918,7 @@
         <v>1.02</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>1.2</v>
@@ -2029,10 +1937,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>docosapentaenoic_acid_omega_3</t>
-        </is>
+      <c r="A48" t="str">
+        <v>docosapentaenoic_acid_omega_3</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
@@ -2046,12 +1952,12 @@
       <c r="E48" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
       <c r="H48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="5" t="inlineStr"/>
+      <c r="I48" s="5"/>
       <c r="J48" s="2" t="n">
         <v>142239</v>
       </c>
@@ -2060,10 +1966,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>mediterranean_diet</t>
-        </is>
+      <c r="A49" t="str">
+        <v>mediterranean_diet</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>2</v>
@@ -2077,12 +1981,12 @@
       <c r="E49" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
       <c r="H49" s="4" t="n">
         <v>69.5</v>
       </c>
-      <c r="I49" s="5" t="inlineStr"/>
+      <c r="I49" s="5"/>
       <c r="J49" s="2" t="n">
         <v>106146</v>
       </c>
@@ -2091,10 +1995,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
+      <c r="A50" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
@@ -2108,12 +2010,12 @@
       <c r="E50" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
       <c r="H50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I50" s="5" t="inlineStr"/>
+      <c r="I50" s="5"/>
       <c r="J50" s="2" t="n">
         <v>142239</v>
       </c>
@@ -2122,10 +2024,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>gondoic_acid</t>
-        </is>
+      <c r="A51" t="str">
+        <v>gondoic_acid</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
@@ -2139,12 +2039,12 @@
       <c r="E51" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
       <c r="H51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="5" t="inlineStr"/>
+      <c r="I51" s="5"/>
       <c r="J51" s="2" t="n">
         <v>142239</v>
       </c>
@@ -2153,10 +2053,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A52" t="str">
+        <v>betaine</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
@@ -2170,12 +2068,12 @@
       <c r="E52" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
       <c r="H52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="5" t="inlineStr"/>
+      <c r="I52" s="5"/>
       <c r="J52" s="2" t="n">
         <v>47896</v>
       </c>
@@ -2184,10 +2082,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A53" t="str">
+        <v>choline</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
@@ -2201,12 +2097,12 @@
       <c r="E53" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
       <c r="H53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="5" t="inlineStr"/>
+      <c r="I53" s="5"/>
       <c r="J53" s="2" t="n">
         <v>6528</v>
       </c>
@@ -2215,10 +2111,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>iron</t>
-        </is>
+      <c r="A54" t="str">
+        <v>iron</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>4</v>
@@ -2227,7 +2121,7 @@
         <v>1.02</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>1.1</v>
@@ -2239,7 +2133,7 @@
         <v>1.33</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>65.9</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>0.4774560014636259</v>
@@ -2252,10 +2146,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A55" t="str">
+        <v>selenium</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>10</v>
@@ -2270,7 +2162,7 @@
         <v>1.12</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>1.28</v>
@@ -2289,91 +2181,91 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>vitamin_k1</t>
-        </is>
+      <c r="A56" t="str">
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>1.02</v>
       </c>
       <c r="D56" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.4142673366090839</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>248736</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>13760</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>vitamin_k1</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D57" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="2" t="n">
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="5"/>
+      <c r="J57" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K56" s="2" t="n">
+      <c r="K57" s="2" t="n">
         <v>268</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>saw_palmetto</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="3" t="n">
+    <row r="58">
+      <c r="A58" t="str">
+        <v>saw_palmetto</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="2" t="n">
-        <v>35239</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>glucosamine</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
       <c r="H58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I58" s="5" t="inlineStr"/>
+      <c r="I58" s="5"/>
       <c r="J58" s="2" t="n">
         <v>35239</v>
       </c>
@@ -2382,29 +2274,27 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>chondroitin</t>
-        </is>
+      <c r="A59" t="str">
+        <v>glucosamine</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
       <c r="H59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="5" t="inlineStr"/>
+      <c r="I59" s="5"/>
       <c r="J59" s="2" t="n">
         <v>35239</v>
       </c>
@@ -2413,41 +2303,37 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
+      <c r="A60" t="str">
+        <v>chondroitin</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
+        <v>1.21</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
       <c r="H60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I60" s="5" t="inlineStr"/>
+      <c r="I60" s="5"/>
       <c r="J60" s="2" t="n">
-        <v>43112</v>
+        <v>35239</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>6058</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>magnesium</t>
-        </is>
+      <c r="A61" t="str">
+        <v>copper</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>1</v>
@@ -2461,12 +2347,12 @@
       <c r="E61" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
       <c r="H61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="5" t="inlineStr"/>
+      <c r="I61" s="5"/>
       <c r="J61" s="2" t="n">
         <v>43112</v>
       </c>
@@ -2475,206 +2361,186 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A62" t="str">
+        <v>magnesium</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>1.06</v>
       </c>
       <c r="D62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5"/>
+      <c r="J62" s="2" t="n">
+        <v>43112</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>6058</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>omega_3_fatty_acids</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D63" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E63" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="F63" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="G62" s="3" t="n">
+      <c r="G63" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>82.8</v>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="I63" s="5" t="n">
         <v>0.1705899002702172</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J63" s="2" t="n">
         <v>607190</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="K63" s="2" t="n">
         <v>20690</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>antioxidants</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
+    <row r="64">
+      <c r="A64" t="str">
+        <v>antioxidants</v>
+      </c>
+      <c r="B64" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="4" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="2" t="n">
-        <v>50507</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>7155</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>butyric_acid</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>1.08</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
+        <v>1.54</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
       <c r="H64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="5" t="inlineStr"/>
+        <v>90.7</v>
+      </c>
+      <c r="I64" s="5"/>
       <c r="J64" s="2" t="n">
-        <v>142239</v>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
+        <v>50507</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>7155</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>omega_9_fatty_acids</t>
-        </is>
+      <c r="A65" t="str">
+        <v>butyric_acid</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>1.08</v>
       </c>
       <c r="D65" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="5"/>
+      <c r="J65" s="2" t="n">
+        <v>142239</v>
+      </c>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>omega_9_fatty_acids</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D66" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E66" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="4" t="n">
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="4" t="n">
         <v>44.6</v>
       </c>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="2" t="n">
+      <c r="I66" s="5"/>
+      <c r="J66" s="2" t="n">
         <v>200518</v>
       </c>
-      <c r="K65" s="2" t="n">
+      <c r="K66" s="2" t="n">
         <v>7678</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="3" t="n">
+    <row r="67">
+      <c r="A67" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E67" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="2" t="n">
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="5"/>
+      <c r="J67" s="2" t="n">
         <v>21533</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="K67" s="2" t="n">
         <v>291</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>ultra_processed_food_intake</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>19.09</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>0.5701786686486264</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>4983</v>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>2932</v>
-      </c>
-    </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>whole_grain_intake</t>
-        </is>
+      <c r="A68" t="str">
+        <v>whole_grain_intake</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>3</v>
@@ -2708,10 +2574,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>phosphorus</t>
-        </is>
+      <c r="A69" t="str">
+        <v>phosphorus</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>1</v>
@@ -2725,12 +2589,12 @@
       <c r="E69" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
       <c r="H69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="5" t="inlineStr"/>
+      <c r="I69" s="5"/>
       <c r="J69" s="2" t="n">
         <v>47885</v>
       </c>
@@ -2739,10 +2603,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A70" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>5</v>
@@ -2776,10 +2638,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A71" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>10</v>
@@ -2813,10 +2673,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>multivitamin</t>
-        </is>
+      <c r="A72" t="str">
+        <v>multivitamin</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>4</v>
@@ -2850,10 +2708,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
+      <c r="A73" t="str">
+        <v>zinc</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>9</v>
@@ -2887,10 +2743,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A74" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>29</v>
@@ -2911,7 +2765,7 @@
         <v>1.66</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>86.6</v>
       </c>
       <c r="I74" s="5" t="n">
         <v>0.005523619063522766</v>
@@ -2919,13 +2773,11 @@
       <c r="J74" s="2" t="n">
         <v>1934957</v>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="K74" s="2"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A75" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>13</v>
@@ -2940,7 +2792,7 @@
         <v>1.36</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>1.81</v>
@@ -2954,13 +2806,11 @@
       <c r="J75" s="2" t="n">
         <v>673771</v>
       </c>
-      <c r="K75" s="2" t="inlineStr"/>
+      <c r="K75" s="2"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
+      <c r="A76" t="str">
+        <v>dairy</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>24</v>
@@ -2994,10 +2844,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
+      <c r="A77" t="str">
+        <v>calcium</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>19</v>
@@ -3018,7 +2866,7 @@
         <v>1.72</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>70.9</v>
       </c>
       <c r="I77" s="5" t="n">
         <v>0.04484903666718714</v>
@@ -3026,13 +2874,11 @@
       <c r="J77" s="2" t="n">
         <v>770289</v>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
+      <c r="K77" s="2"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A78" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>3</v>
@@ -3066,10 +2912,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A79" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>7</v>
@@ -3090,7 +2934,7 @@
         <v>2.01</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>87.1</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>0.02035566769413239</v>
@@ -3098,13 +2942,11 @@
       <c r="J79" s="2" t="n">
         <v>255429</v>
       </c>
-      <c r="K79" s="2" t="inlineStr"/>
+      <c r="K79" s="2"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>alpha_linolenic_acid</t>
-        </is>
+      <c r="A80" t="str">
+        <v>alpha_linolenic_acid</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>6</v>
@@ -3138,10 +2980,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>mineral_supplements</t>
-        </is>
+      <c r="A81" t="str">
+        <v>mineral_supplements</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>2</v>
@@ -3155,12 +2995,12 @@
       <c r="E81" s="3" t="n">
         <v>2.26</v>
       </c>
-      <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
       <c r="H81" s="4" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="I81" s="5" t="inlineStr"/>
+        <v>80.1</v>
+      </c>
+      <c r="I81" s="5"/>
       <c r="J81" s="2" t="n">
         <v>57251</v>
       </c>
@@ -3169,10 +3009,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A82" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>3</v>
@@ -3193,7 +3031,7 @@
         <v>159.52</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>91.9</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>0.6751776574754227</v>
@@ -3206,10 +3044,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>chocolate</t>
-        </is>
+      <c r="A83" t="str">
+        <v>chocolate</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>1</v>
@@ -3223,12 +3059,12 @@
       <c r="E83" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
       <c r="H83" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="5" t="inlineStr"/>
+      <c r="I83" s="5"/>
       <c r="J83" s="2" t="n">
         <v>2611</v>
       </c>
@@ -3237,10 +3073,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>western_pattern_diet</t>
-        </is>
+      <c r="A84" t="str">
+        <v>western_pattern_diet</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>2</v>
@@ -3254,12 +3088,12 @@
       <c r="E84" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
       <c r="H84" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="I84" s="5" t="inlineStr"/>
+      <c r="I84" s="5"/>
       <c r="J84" s="2" t="n">
         <v>44462</v>
       </c>
@@ -3268,10 +3102,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>fermented_foods</t>
-        </is>
+      <c r="A85" t="str">
+        <v>fermented_foods</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>3</v>
@@ -3289,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>664.3099999999999</v>
+        <v>664.31</v>
       </c>
       <c r="H85" s="4" t="n">
         <v>62</v>
@@ -3305,10 +3137,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
+      <c r="A86" t="str">
+        <v>oleic_acid</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>1</v>
@@ -3322,12 +3152,12 @@
       <c r="E86" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
       <c r="H86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="5" t="inlineStr"/>
+      <c r="I86" s="5"/>
       <c r="J86" s="2" t="n">
         <v>58279</v>
       </c>
@@ -3336,10 +3166,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>vitamin_b12</t>
-        </is>
+      <c r="A87" t="str">
+        <v>vitamin_b12</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>2</v>
@@ -3353,12 +3181,12 @@
       <c r="E87" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="F87" s="3" t="inlineStr"/>
-      <c r="G87" s="3" t="inlineStr"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
       <c r="H87" s="4" t="n">
         <v>24.7</v>
       </c>
-      <c r="I87" s="5" t="inlineStr"/>
+      <c r="I87" s="5"/>
       <c r="J87" s="2" t="n">
         <v>719</v>
       </c>
@@ -3367,10 +3195,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A88" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>14</v>
@@ -3391,7 +3217,7 @@
         <v>4.51</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>89.6</v>
       </c>
       <c r="I88" s="5" t="n">
         <v>0.01959176169058006</v>
@@ -3404,10 +3230,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>pickled_vegetables</t>
-        </is>
+      <c r="A89" t="str">
+        <v>pickled_vegetables</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>1</v>
@@ -3421,12 +3245,12 @@
       <c r="E89" s="3" t="n">
         <v>5.94</v>
       </c>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
       <c r="H89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I89" s="5" t="inlineStr"/>
+      <c r="I89" s="5"/>
       <c r="J89" s="2" t="n">
         <v>404</v>
       </c>

--- a/summary/yes/exposures_meta_analysis_prostate_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_prostate_cancer_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,8 +509,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>vitamin_b1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -524,12 +526,12 @@
       <c r="E2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="2" t="n">
         <v>204</v>
       </c>
@@ -538,8 +540,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>natto</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>natto</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -553,12 +557,12 @@
       <c r="E3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>280</v>
       </c>
@@ -567,8 +571,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>papaya</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>papaya</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -582,12 +588,12 @@
       <c r="E4" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>105</v>
       </c>
@@ -596,8 +602,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>early_time_restricted_eating</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>early_time_restricted_eating</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -611,12 +619,12 @@
       <c r="E5" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>1455</v>
       </c>
@@ -625,8 +633,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>soy</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>soy</t>
+        </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>8</v>
@@ -647,7 +657,7 @@
         <v>2.09</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>78.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0.1010785350953814</v>
@@ -660,8 +670,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>green_tea</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>7</v>
@@ -685,7 +697,7 @@
         <v>72.7</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.1767576153047421</v>
+        <v>0.1767576153047418</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>99090</v>
@@ -695,8 +707,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>3</v>
@@ -717,7 +731,7 @@
         <v>206.11</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>74.9</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0.1151715356999109</v>
@@ -725,11 +739,13 @@
       <c r="J8" s="2" t="n">
         <v>101084</v>
       </c>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>low_fat_diet</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>low_fat_diet</t>
+        </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -743,12 +759,12 @@
       <c r="E9" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="2" t="n">
         <v>1170</v>
       </c>
@@ -757,8 +773,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>lutein</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>2</v>
@@ -772,12 +790,12 @@
       <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="2" t="n">
         <v>1623</v>
       </c>
@@ -786,8 +804,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>vitamin_k</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>vitamin_k</t>
+        </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -801,12 +821,12 @@
       <c r="E11" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="2" t="n">
         <v>11319</v>
       </c>
@@ -815,8 +835,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>vitamin_k2</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vitamin_k2</t>
+        </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -830,12 +852,12 @@
       <c r="E12" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="2" t="n">
         <v>11319</v>
       </c>
@@ -844,8 +866,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>quercetin</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -859,12 +883,12 @@
       <c r="E13" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="2" t="n">
         <v>971</v>
       </c>
@@ -873,8 +897,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>vegan_diet</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>vegan_diet</t>
+        </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -888,12 +914,12 @@
       <c r="E14" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="2" t="n">
         <v>26346</v>
       </c>
@@ -902,14 +928,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>garlic</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.42</v>
@@ -937,8 +965,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>vegetarian_diet</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vegetarian_diet</t>
+        </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -947,17 +977,17 @@
         <v>0.7</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="2" t="n">
         <v>217937</v>
       </c>
@@ -966,8 +996,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>tomato</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>11</v>
@@ -988,10 +1020,10 @@
         <v>1.16</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>78.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.00002045420729252852</v>
+        <v>2.045420729252859e-05</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1057923</v>
@@ -1001,8 +1033,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>tea</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>10</v>
@@ -1023,10 +1057,10 @@
         <v>1.27</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>84.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.04996208468350858</v>
+        <v>0.04996208468350857</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>314398</v>
@@ -1036,8 +1070,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>zeaxanthin</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1051,12 +1087,12 @@
       <c r="E19" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="2" t="n">
         <v>652</v>
       </c>
@@ -1065,8 +1101,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>potassium</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1080,12 +1118,12 @@
       <c r="E20" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
         <v>656</v>
       </c>
@@ -1094,8 +1132,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>genistein</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>genistein</t>
+        </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>3</v>
@@ -1119,7 +1159,7 @@
         <v>85</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.05600670850526825</v>
+        <v>0.05600670850526847</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>70911</v>
@@ -1129,8 +1169,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>iodine</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>iodine</t>
+        </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1144,12 +1186,12 @@
       <c r="E22" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="5"/>
+      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="2" t="n">
         <v>656</v>
       </c>
@@ -1158,8 +1200,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>beta_carotene</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>10</v>
@@ -1183,16 +1227,18 @@
         <v>64.5</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.04074875994005019</v>
+        <v>0.04074875994005018</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>94949</v>
       </c>
-      <c r="K23" s="2"/>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>time_restricted_eating</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>time_restricted_eating</t>
+        </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1206,12 +1252,12 @@
       <c r="E24" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
         <v>1455</v>
       </c>
@@ -1220,8 +1266,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>linoleic_acid</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1235,12 +1283,12 @@
       <c r="E25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="2" t="n">
         <v>2745</v>
       </c>
@@ -1249,8 +1297,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>omega_6_fatty_acids</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>omega_6_fatty_acids</t>
+        </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1264,12 +1314,12 @@
       <c r="E26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="2" t="n">
         <v>2745</v>
       </c>
@@ -1278,8 +1328,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>mushrooms</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mushrooms</t>
+        </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1293,12 +1345,12 @@
       <c r="E27" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>36499</v>
       </c>
@@ -1307,8 +1359,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>vitamin_c</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>10</v>
@@ -1342,8 +1396,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>lycopene</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>13</v>
@@ -1377,8 +1433,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>folic_acid</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>5</v>
@@ -1402,16 +1460,18 @@
         <v>55.4</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.7901812753667304</v>
+        <v>0.7901812753667296</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>131386</v>
       </c>
-      <c r="K30" s="2"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>legumes</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>legumes</t>
+        </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>8</v>
@@ -1420,7 +1480,7 @@
         <v>0.89</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0.97</v>
@@ -1435,7 +1495,7 @@
         <v>62.4</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0.006170430008920979</v>
+        <v>0.00617043000892098</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1155076</v>
@@ -1445,8 +1505,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>soluble_dietary_fiber_intake</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>soluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>3</v>
@@ -1470,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.188399637329524</v>
+        <v>0.1883996373295245</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>80888</v>
@@ -1480,8 +1542,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>vitamin_b6</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>3</v>
@@ -1515,8 +1579,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>plant_based_diet</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>plant_based_diet</t>
+        </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>2</v>
@@ -1530,12 +1596,12 @@
       <c r="E34" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="I34" s="5"/>
+      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="2" t="n">
         <v>211318</v>
       </c>
@@ -1544,8 +1610,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>caffeine</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>caffeine</t>
+        </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -1559,12 +1627,12 @@
       <c r="E35" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
         <v>46667</v>
       </c>
@@ -1573,8 +1641,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>ginseng</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ginseng</t>
+        </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1588,12 +1658,12 @@
       <c r="E36" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5"/>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
         <v>35239</v>
       </c>
@@ -1602,8 +1672,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>total_dietary_fiber_intake</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>7</v>
@@ -1627,7 +1699,7 @@
         <v>42.9</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.07744276379719466</v>
+        <v>0.0774427637971946</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>972077</v>
@@ -1637,8 +1709,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>dash_diet</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>dash_diet</t>
+        </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>2</v>
@@ -1652,20 +1726,22 @@
       <c r="E38" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
       <c r="H38" s="4" t="n">
-        <v>73.9</v>
-      </c>
-      <c r="I38" s="5"/>
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
         <v>152714</v>
       </c>
-      <c r="K38" s="2"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>ginkgo_biloba</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ginkgo_biloba</t>
+        </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
@@ -1679,12 +1755,12 @@
       <c r="E39" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="I39" s="5"/>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
         <v>38308</v>
       </c>
@@ -1693,14 +1769,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>coenzyme_q10</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>coenzyme_q10</t>
+        </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0.76</v>
@@ -1708,12 +1786,12 @@
       <c r="E40" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="5"/>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
         <v>35239</v>
       </c>
@@ -1722,8 +1800,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>eicosapentaenoic_acid</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>eicosapentaenoic_acid</t>
+        </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>2</v>
@@ -1737,12 +1817,12 @@
       <c r="E41" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="I41" s="5"/>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="2" t="n">
         <v>430507</v>
       </c>
@@ -1751,8 +1831,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>vitamin_e</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>13</v>
@@ -1773,10 +1855,10 @@
         <v>1.34</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>73.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.116278835132563</v>
+        <v>0.1162788351325632</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>270107</v>
@@ -1786,8 +1868,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>fish_oil</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fish_oil</t>
+        </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1801,12 +1885,12 @@
       <c r="E43" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="5"/>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="2" t="n">
         <v>35239</v>
       </c>
@@ -1815,8 +1899,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>plant_protein_intake</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>plant_protein_intake</t>
+        </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1830,12 +1916,12 @@
       <c r="E44" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="5"/>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="2" t="n">
         <v>150671</v>
       </c>
@@ -1844,8 +1930,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>animal_protein_intake</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -1854,17 +1942,17 @@
         <v>0.99</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="5"/>
+      <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="2" t="n">
         <v>159482</v>
       </c>
@@ -1873,8 +1961,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>dietary_protein_intake</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>2</v>
@@ -1888,12 +1978,12 @@
       <c r="E46" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="5"/>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="2" t="n">
         <v>109557</v>
       </c>
@@ -1902,8 +1992,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>eggs</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>3</v>
@@ -1918,7 +2010,7 @@
         <v>1.02</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>1.2</v>
@@ -1937,8 +2029,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
-        <v>docosapentaenoic_acid_omega_3</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>docosapentaenoic_acid_omega_3</t>
+        </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
@@ -1952,12 +2046,12 @@
       <c r="E48" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="5"/>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="2" t="n">
         <v>142239</v>
       </c>
@@ -1966,8 +2060,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>mediterranean_diet</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>mediterranean_diet</t>
+        </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>2</v>
@@ -1981,12 +2077,12 @@
       <c r="E49" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="4" t="n">
         <v>69.5</v>
       </c>
-      <c r="I49" s="5"/>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="2" t="n">
         <v>106146</v>
       </c>
@@ -1995,8 +2091,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>docosahexaenoic_acid</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
@@ -2010,12 +2108,12 @@
       <c r="E50" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I50" s="5"/>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="2" t="n">
         <v>142239</v>
       </c>
@@ -2024,8 +2122,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
-        <v>gondoic_acid</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>gondoic_acid</t>
+        </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
@@ -2039,12 +2139,12 @@
       <c r="E51" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="5"/>
+      <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="2" t="n">
         <v>142239</v>
       </c>
@@ -2053,8 +2153,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str">
-        <v>betaine</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
@@ -2068,12 +2170,12 @@
       <c r="E52" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="5"/>
+      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="2" t="n">
         <v>47896</v>
       </c>
@@ -2082,8 +2184,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
-        <v>choline</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
@@ -2097,12 +2201,12 @@
       <c r="E53" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="5"/>
+      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="2" t="n">
         <v>6528</v>
       </c>
@@ -2111,8 +2215,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="str">
-        <v>iron</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>4</v>
@@ -2121,7 +2227,7 @@
         <v>1.02</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>1.1</v>
@@ -2133,10 +2239,10 @@
         <v>1.33</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>65.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>0.4774560014636259</v>
+        <v>0.4774560014636261</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>183783</v>
@@ -2146,8 +2252,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str">
-        <v>selenium</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>10</v>
@@ -2162,7 +2270,7 @@
         <v>1.12</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>1.28</v>
@@ -2171,7 +2279,7 @@
         <v>43.6</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>0.08106606109529828</v>
+        <v>0.08106606109529818</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>235441</v>
@@ -2181,8 +2289,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
-        <v>ultra_processed_food_intake</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>6</v>
@@ -2206,7 +2316,7 @@
         <v>38.1</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>0.4142673366090839</v>
+        <v>0.4142673366090832</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>248736</v>
@@ -2216,8 +2326,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
-        <v>vitamin_k1</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>vitamin_k1</t>
+        </is>
       </c>
       <c r="B57" s="2" t="n">
         <v>1</v>
@@ -2231,12 +2343,12 @@
       <c r="E57" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
       <c r="H57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="5"/>
+      <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="2" t="n">
         <v>11319</v>
       </c>
@@ -2245,8 +2357,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str">
-        <v>saw_palmetto</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>saw_palmetto</t>
+        </is>
       </c>
       <c r="B58" s="2" t="n">
         <v>1</v>
@@ -2260,12 +2374,12 @@
       <c r="E58" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
       <c r="H58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I58" s="5"/>
+      <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="2" t="n">
         <v>35239</v>
       </c>
@@ -2274,8 +2388,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str">
-        <v>glucosamine</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>glucosamine</t>
+        </is>
       </c>
       <c r="B59" s="2" t="n">
         <v>1</v>
@@ -2289,12 +2405,12 @@
       <c r="E59" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="5"/>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="2" t="n">
         <v>35239</v>
       </c>
@@ -2303,8 +2419,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str">
-        <v>chondroitin</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>chondroitin</t>
+        </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>1</v>
@@ -2318,12 +2436,12 @@
       <c r="E60" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
       <c r="H60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I60" s="5"/>
+      <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="2" t="n">
         <v>35239</v>
       </c>
@@ -2332,8 +2450,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="str">
-        <v>copper</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
       </c>
       <c r="B61" s="2" t="n">
         <v>1</v>
@@ -2347,12 +2467,12 @@
       <c r="E61" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="5"/>
+      <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="2" t="n">
         <v>43112</v>
       </c>
@@ -2361,8 +2481,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="str">
-        <v>magnesium</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>magnesium</t>
+        </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>1</v>
@@ -2376,12 +2498,12 @@
       <c r="E62" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="5"/>
+      <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="2" t="n">
         <v>43112</v>
       </c>
@@ -2390,8 +2512,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="str">
-        <v>omega_3_fatty_acids</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
       </c>
       <c r="B63" s="2" t="n">
         <v>8</v>
@@ -2425,8 +2549,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="str">
-        <v>antioxidants</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>antioxidants</t>
+        </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>2</v>
@@ -2440,12 +2566,12 @@
       <c r="E64" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
       <c r="H64" s="4" t="n">
         <v>90.7</v>
       </c>
-      <c r="I64" s="5"/>
+      <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="2" t="n">
         <v>50507</v>
       </c>
@@ -2454,8 +2580,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
-        <v>butyric_acid</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>butyric_acid</t>
+        </is>
       </c>
       <c r="B65" s="2" t="n">
         <v>1</v>
@@ -2469,20 +2597,22 @@
       <c r="E65" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
       <c r="H65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I65" s="5"/>
+      <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K65" s="2"/>
+      <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="str">
-        <v>omega_9_fatty_acids</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>omega_9_fatty_acids</t>
+        </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>2</v>
@@ -2496,12 +2626,12 @@
       <c r="E66" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
       <c r="H66" s="4" t="n">
         <v>44.6</v>
       </c>
-      <c r="I66" s="5"/>
+      <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="2" t="n">
         <v>200518</v>
       </c>
@@ -2510,8 +2640,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
       </c>
       <c r="B67" s="2" t="n">
         <v>1</v>
@@ -2525,12 +2657,12 @@
       <c r="E67" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I67" s="5"/>
+      <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="2" t="n">
         <v>21533</v>
       </c>
@@ -2539,8 +2671,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="str">
-        <v>whole_grain_intake</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>whole_grain_intake</t>
+        </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>3</v>
@@ -2574,8 +2708,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="str">
-        <v>phosphorus</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>phosphorus</t>
+        </is>
       </c>
       <c r="B69" s="2" t="n">
         <v>1</v>
@@ -2589,12 +2725,12 @@
       <c r="E69" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
       <c r="H69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="5"/>
+      <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="2" t="n">
         <v>47885</v>
       </c>
@@ -2603,8 +2739,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="str">
-        <v>vitamin_a</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>5</v>
@@ -2628,7 +2766,7 @@
         <v>89.2</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>0.00132463054799409</v>
+        <v>0.001324630547994087</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>3207</v>
@@ -2638,8 +2776,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="str">
-        <v>processed_meat_intake</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
       </c>
       <c r="B71" s="2" t="n">
         <v>10</v>
@@ -2663,7 +2803,7 @@
         <v>71.2</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0.002637956795546257</v>
+        <v>0.002637956795546261</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>1091655</v>
@@ -2673,8 +2813,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="str">
-        <v>multivitamin</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>multivitamin</t>
+        </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>4</v>
@@ -2708,8 +2850,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="str">
-        <v>zinc</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
       </c>
       <c r="B73" s="2" t="n">
         <v>9</v>
@@ -2733,7 +2877,7 @@
         <v>71.2</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.8512478924325503</v>
+        <v>0.8512478924325507</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>94876</v>
@@ -2743,8 +2887,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="str">
-        <v>alcohol</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>29</v>
@@ -2765,19 +2911,21 @@
         <v>1.66</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>86.6</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>0.005523619063522766</v>
+        <v>0.00552361906352278</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1934957</v>
       </c>
-      <c r="K74" s="2"/>
+      <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="str">
-        <v>polyunsaturated_fat_pufa</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
       </c>
       <c r="B75" s="2" t="n">
         <v>13</v>
@@ -2792,7 +2940,7 @@
         <v>1.36</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>1.81</v>
@@ -2801,16 +2949,18 @@
         <v>86</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>0.007502544100791494</v>
+        <v>0.007502544100791496</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>673771</v>
       </c>
-      <c r="K75" s="2"/>
+      <c r="K75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="str">
-        <v>dairy</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>24</v>
@@ -2834,7 +2984,7 @@
         <v>82.7</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>0.09941545468620652</v>
+        <v>0.09941545468620654</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>739672</v>
@@ -2844,8 +2994,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="str">
-        <v>calcium</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
       </c>
       <c r="B77" s="2" t="n">
         <v>19</v>
@@ -2866,19 +3018,21 @@
         <v>1.72</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>70.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.04484903666718714</v>
+        <v>0.04484903666718717</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>770289</v>
       </c>
-      <c r="K77" s="2"/>
+      <c r="K77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="str">
-        <v>yogurt</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
       </c>
       <c r="B78" s="2" t="n">
         <v>3</v>
@@ -2912,8 +3066,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="str">
-        <v>monounsaturated_fat_mufa</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
       </c>
       <c r="B79" s="2" t="n">
         <v>7</v>
@@ -2934,19 +3090,21 @@
         <v>2.01</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>87.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>0.02035566769413239</v>
+        <v>0.02035566769413238</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>255429</v>
       </c>
-      <c r="K79" s="2"/>
+      <c r="K79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="str">
-        <v>alpha_linolenic_acid</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>alpha_linolenic_acid</t>
+        </is>
       </c>
       <c r="B80" s="2" t="n">
         <v>6</v>
@@ -2970,7 +3128,7 @@
         <v>88.7</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0.02622839085694528</v>
+        <v>0.02622839085694529</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>556471</v>
@@ -2980,8 +3138,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="str">
-        <v>mineral_supplements</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>mineral_supplements</t>
+        </is>
       </c>
       <c r="B81" s="2" t="n">
         <v>2</v>
@@ -2995,12 +3155,12 @@
       <c r="E81" s="3" t="n">
         <v>2.26</v>
       </c>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="4" t="n">
-        <v>80.1</v>
-      </c>
-      <c r="I81" s="5"/>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="2" t="n">
         <v>57251</v>
       </c>
@@ -3009,8 +3169,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="str">
-        <v>vitamin_d</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
       </c>
       <c r="B82" s="2" t="n">
         <v>3</v>
@@ -3031,10 +3193,10 @@
         <v>159.52</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>91.9</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>0.6751776574754227</v>
+        <v>0.6751776574754228</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>247791</v>
@@ -3044,8 +3206,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="str">
-        <v>chocolate</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>chocolate</t>
+        </is>
       </c>
       <c r="B83" s="2" t="n">
         <v>1</v>
@@ -3059,12 +3223,12 @@
       <c r="E83" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
       <c r="H83" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="5"/>
+      <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="2" t="n">
         <v>2611</v>
       </c>
@@ -3073,8 +3237,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="str">
-        <v>western_pattern_diet</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>western_pattern_diet</t>
+        </is>
       </c>
       <c r="B84" s="2" t="n">
         <v>2</v>
@@ -3088,12 +3254,12 @@
       <c r="E84" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
       <c r="H84" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="I84" s="5"/>
+      <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="2" t="n">
         <v>44462</v>
       </c>
@@ -3102,8 +3268,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="str">
-        <v>fermented_foods</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fermented_foods</t>
+        </is>
       </c>
       <c r="B85" s="2" t="n">
         <v>3</v>
@@ -3121,13 +3289,13 @@
         <v>0</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>664.31</v>
+        <v>664.3099999999999</v>
       </c>
       <c r="H85" s="4" t="n">
         <v>62</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>0.1814798483236068</v>
+        <v>0.1814798483236069</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>3460</v>
@@ -3137,8 +3305,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="str">
-        <v>oleic_acid</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
       </c>
       <c r="B86" s="2" t="n">
         <v>1</v>
@@ -3152,12 +3322,12 @@
       <c r="E86" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
       <c r="H86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="5"/>
+      <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="2" t="n">
         <v>58279</v>
       </c>
@@ -3166,8 +3336,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="str">
-        <v>vitamin_b12</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>vitamin_b12</t>
+        </is>
       </c>
       <c r="B87" s="2" t="n">
         <v>2</v>
@@ -3181,12 +3353,12 @@
       <c r="E87" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr"/>
       <c r="H87" s="4" t="n">
         <v>24.7</v>
       </c>
-      <c r="I87" s="5"/>
+      <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="2" t="n">
         <v>719</v>
       </c>
@@ -3195,8 +3367,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="str">
-        <v>red_meat</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
       </c>
       <c r="B88" s="2" t="n">
         <v>14</v>
@@ -3217,10 +3391,10 @@
         <v>4.51</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>89.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>0.01959176169058006</v>
+        <v>0.01959176169058002</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>974550</v>
@@ -3230,8 +3404,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="str">
-        <v>pickled_vegetables</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>pickled_vegetables</t>
+        </is>
       </c>
       <c r="B89" s="2" t="n">
         <v>1</v>
@@ -3245,12 +3421,12 @@
       <c r="E89" s="3" t="n">
         <v>5.94</v>
       </c>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I89" s="5"/>
+      <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="2" t="n">
         <v>404</v>
       </c>

--- a/summary/yes/exposures_meta_analysis_prostate_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_prostate_cancer_dietary.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -452,57 +464,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -514,28 +526,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>102</v>
       </c>
     </row>
@@ -545,28 +557,28 @@
           <t>natto</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>140</v>
       </c>
     </row>
@@ -576,28 +588,28 @@
           <t>papaya</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>35</v>
       </c>
     </row>
@@ -607,28 +619,28 @@
           <t>early_time_restricted_eating</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>607</v>
       </c>
     </row>
@@ -638,34 +650,34 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>0.1010785350953814</v>
-      </c>
-      <c r="J6" s="2" t="n">
+      <c r="I6" s="6" t="n">
+        <v>0.1010785350953813</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>85059</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>5399</v>
       </c>
     </row>
@@ -675,34 +687,34 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>72.7</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0.1767576153047418</v>
-      </c>
-      <c r="J7" s="2" t="n">
+      <c r="I7" s="6" t="n">
+        <v>0.1767576153047416</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>99090</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>1577</v>
       </c>
     </row>
@@ -712,34 +724,34 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>206.11</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.1151715356999109</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>101084</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -747,28 +759,28 @@
           <t>low_fat_diet</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="2" t="n">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="3" t="n">
         <v>1170</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>390</v>
       </c>
     </row>
@@ -778,28 +790,28 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
         <v>1623</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>677</v>
       </c>
     </row>
@@ -809,28 +821,28 @@
           <t>vitamin_k</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="B11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -840,28 +852,28 @@
           <t>vitamin_k2</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -871,28 +883,28 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="B13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>971</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>433</v>
       </c>
     </row>
@@ -902,28 +914,28 @@
           <t>vegan_diet</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
         <v>26346</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>1079</v>
       </c>
     </row>
@@ -933,34 +945,34 @@
           <t>garlic</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>265.07</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I15" s="6" t="n">
         <v>0.2044018200861738</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="3" t="n">
         <v>36604</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -970,28 +982,28 @@
           <t>vegetarian_diet</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3" t="n">
+      <c r="B16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="2" t="n">
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>217937</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>9501</v>
       </c>
     </row>
@@ -1001,34 +1013,34 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I17" s="6" t="n">
         <v>2.045420729252859e-05</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="3" t="n">
         <v>1057923</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>67108</v>
       </c>
     </row>
@@ -1038,34 +1050,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>0.04996208468350857</v>
-      </c>
-      <c r="J18" s="2" t="n">
+      <c r="I18" s="6" t="n">
+        <v>0.0499620846835085</v>
+      </c>
+      <c r="J18" s="3" t="n">
         <v>314398</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>15389</v>
       </c>
     </row>
@@ -1075,28 +1087,28 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
         <v>652</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>244</v>
       </c>
     </row>
@@ -1106,28 +1118,28 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="2" t="n">
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1137,34 +1149,34 @@
           <t>genistein</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>6253.84</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="I21" s="5" t="n">
-        <v>0.05600670850526847</v>
-      </c>
-      <c r="J21" s="2" t="n">
+      <c r="I21" s="6" t="n">
+        <v>0.05600670850526827</v>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>70911</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>727</v>
       </c>
     </row>
@@ -1174,28 +1186,28 @@
           <t>iodine</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="2" t="n">
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1205,34 +1217,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="4" t="n">
         <v>1.51</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="5" t="n">
         <v>64.5</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>0.04074875994005018</v>
-      </c>
-      <c r="J23" s="2" t="n">
+      <c r="I23" s="6" t="n">
+        <v>0.04074875994005017</v>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>94949</v>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1240,28 +1252,28 @@
           <t>time_restricted_eating</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3" t="n">
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="2" t="n">
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>607</v>
       </c>
     </row>
@@ -1271,28 +1283,28 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3" t="n">
+      <c r="B25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="2" t="n">
+      <c r="E25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="3" t="n">
         <v>2745</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1302,28 +1314,28 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="2" t="n">
+      <c r="E26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
         <v>2745</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1333,28 +1345,28 @@
           <t>mushrooms</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="2" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>36499</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -1364,34 +1376,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="5" t="n">
         <v>80.7</v>
       </c>
-      <c r="I28" s="5" t="n">
-        <v>0.8930041904516864</v>
-      </c>
-      <c r="J28" s="2" t="n">
+      <c r="I28" s="6" t="n">
+        <v>0.8930041904516861</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>68446</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>7637</v>
       </c>
     </row>
@@ -1401,34 +1413,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="5" t="n">
         <v>69.5</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>0.07495549929133036</v>
-      </c>
-      <c r="J29" s="2" t="n">
+      <c r="I29" s="6" t="n">
+        <v>0.0749554992913304</v>
+      </c>
+      <c r="J29" s="3" t="n">
         <v>282888</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>22602</v>
       </c>
     </row>
@@ -1438,34 +1450,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.67</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="5" t="n">
         <v>55.4</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>0.7901812753667296</v>
-      </c>
-      <c r="J30" s="2" t="n">
+      <c r="I30" s="6" t="n">
+        <v>0.7901812753667304</v>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>131386</v>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1473,34 +1485,34 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="5" t="n">
         <v>62.4</v>
       </c>
-      <c r="I31" s="5" t="n">
-        <v>0.00617043000892098</v>
-      </c>
-      <c r="J31" s="2" t="n">
+      <c r="I31" s="6" t="n">
+        <v>0.006170430008920973</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>1155076</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>79072</v>
       </c>
     </row>
@@ -1510,34 +1522,34 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.1883996373295245</v>
-      </c>
-      <c r="J32" s="2" t="n">
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.188399637329524</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>80888</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>10851</v>
       </c>
     </row>
@@ -1547,34 +1559,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0.2443574036478494</v>
-      </c>
-      <c r="J33" s="2" t="n">
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.2443574036478493</v>
+      </c>
+      <c r="J33" s="3" t="n">
         <v>70879</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>7656</v>
       </c>
     </row>
@@ -1584,28 +1596,28 @@
           <t>plant_based_diet</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="4" t="n">
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="5" t="n">
         <v>39.5</v>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="3" t="n">
         <v>211318</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>24516</v>
       </c>
     </row>
@@ -1615,28 +1627,28 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="3" t="n">
+      <c r="B35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="2" t="n">
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="3" t="n">
         <v>46667</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -1646,28 +1658,28 @@
           <t>ginseng</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="3" t="n">
+      <c r="B36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="2" t="n">
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1677,34 +1689,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="n">
+      <c r="E37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="5" t="n">
         <v>42.9</v>
       </c>
-      <c r="I37" s="5" t="n">
-        <v>0.0774427637971946</v>
-      </c>
-      <c r="J37" s="2" t="n">
+      <c r="I37" s="6" t="n">
+        <v>0.07744276379719461</v>
+      </c>
+      <c r="J37" s="3" t="n">
         <v>972077</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>64899</v>
       </c>
     </row>
@@ -1714,28 +1726,28 @@
           <t>dash_diet</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="n">
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="n">
         <v>73.90000000000001</v>
       </c>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
         <v>152714</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1743,28 +1755,28 @@
           <t>ginkgo_biloba</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="n">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="3" t="n">
         <v>38308</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>1665</v>
       </c>
     </row>
@@ -1774,28 +1786,28 @@
           <t>coenzyme_q10</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1805,28 +1817,28 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="4" t="n">
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
         <v>430507</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>7761</v>
       </c>
     </row>
@@ -1836,34 +1848,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="5" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="I42" s="5" t="n">
-        <v>0.1162788351325632</v>
-      </c>
-      <c r="J42" s="2" t="n">
+      <c r="I42" s="6" t="n">
+        <v>0.116278835132563</v>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>270107</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K42" s="3" t="n">
         <v>13301</v>
       </c>
     </row>
@@ -1873,28 +1885,28 @@
           <t>fish_oil</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="3" t="n">
+      <c r="B43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K43" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1904,28 +1916,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="3" t="n">
+      <c r="B44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="3" t="n">
         <v>150671</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K44" s="3" t="n">
         <v>14238</v>
       </c>
     </row>
@@ -1935,28 +1947,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="3" t="n">
+      <c r="B45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="3" t="n">
         <v>159482</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K45" s="3" t="n">
         <v>17349</v>
       </c>
     </row>
@@ -1966,28 +1978,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="3" t="n">
         <v>109557</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K46" s="3" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -1997,34 +2009,34 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="G47" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="H47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5" t="n">
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6" t="n">
         <v>0.8121269612161565</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="3" t="n">
         <v>900752</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K47" s="3" t="n">
         <v>53381</v>
       </c>
     </row>
@@ -2034,28 +2046,28 @@
           <t>docosapentaenoic_acid_omega_3</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="3" t="n">
+      <c r="B48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K48" s="3" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2065,28 +2077,28 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="3" t="n">
+      <c r="C49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="4" t="n">
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="n">
         <v>69.5</v>
       </c>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="3" t="n">
         <v>106146</v>
       </c>
-      <c r="K49" s="2" t="n">
+      <c r="K49" s="3" t="n">
         <v>7476</v>
       </c>
     </row>
@@ -2096,28 +2108,28 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="3" t="n">
+      <c r="B50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="4" t="n">
         <v>1.04</v>
       </c>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="2" t="n">
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K50" s="2" t="n">
+      <c r="K50" s="3" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2127,28 +2139,28 @@
           <t>gondoic_acid</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="3" t="n">
+      <c r="B51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="2" t="n">
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="K51" s="3" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2158,28 +2170,28 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="3" t="n">
+      <c r="B52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="3" t="n">
         <v>47896</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="K52" s="3" t="n">
         <v>695</v>
       </c>
     </row>
@@ -2189,28 +2201,28 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="3" t="n">
+      <c r="B53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="2" t="n">
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="3" t="n">
         <v>6528</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="K53" s="3" t="n">
         <v>811</v>
       </c>
     </row>
@@ -2220,34 +2232,34 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="C54" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="F54" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H54" s="5" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="I54" s="5" t="n">
-        <v>0.4774560014636261</v>
-      </c>
-      <c r="J54" s="2" t="n">
+      <c r="I54" s="6" t="n">
+        <v>0.477456001463626</v>
+      </c>
+      <c r="J54" s="3" t="n">
         <v>183783</v>
       </c>
-      <c r="K54" s="2" t="n">
+      <c r="K54" s="3" t="n">
         <v>11462</v>
       </c>
     </row>
@@ -2257,34 +2269,34 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="F55" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="5" t="n">
         <v>43.6</v>
       </c>
-      <c r="I55" s="5" t="n">
-        <v>0.08106606109529818</v>
-      </c>
-      <c r="J55" s="2" t="n">
+      <c r="I55" s="6" t="n">
+        <v>0.08106606109529807</v>
+      </c>
+      <c r="J55" s="3" t="n">
         <v>235441</v>
       </c>
-      <c r="K55" s="2" t="n">
+      <c r="K55" s="3" t="n">
         <v>18652</v>
       </c>
     </row>
@@ -2294,34 +2306,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F56" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H56" s="5" t="n">
         <v>38.1</v>
       </c>
-      <c r="I56" s="5" t="n">
-        <v>0.4142673366090832</v>
-      </c>
-      <c r="J56" s="2" t="n">
+      <c r="I56" s="6" t="n">
+        <v>0.4142673366090839</v>
+      </c>
+      <c r="J56" s="3" t="n">
         <v>248736</v>
       </c>
-      <c r="K56" s="2" t="n">
+      <c r="K56" s="3" t="n">
         <v>13760</v>
       </c>
     </row>
@@ -2331,28 +2343,28 @@
           <t>vitamin_k1</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="3" t="n">
+      <c r="B57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="2" t="n">
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K57" s="2" t="n">
+      <c r="K57" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2362,28 +2374,28 @@
           <t>saw_palmetto</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="3" t="n">
+      <c r="B58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="2" t="n">
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr"/>
+      <c r="J58" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K58" s="2" t="n">
+      <c r="K58" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2393,28 +2405,28 @@
           <t>glucosamine</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="3" t="n">
+      <c r="B59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="4" t="n">
         <v>1.04</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="2" t="n">
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="K59" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2424,28 +2436,28 @@
           <t>chondroitin</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="3" t="n">
+      <c r="B60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="2" t="n">
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K60" s="2" t="n">
+      <c r="K60" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2455,28 +2467,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="3" t="n">
+      <c r="B61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="D61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="3" t="n">
+      <c r="D61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="2" t="n">
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="3" t="n">
         <v>43112</v>
       </c>
-      <c r="K61" s="2" t="n">
+      <c r="K61" s="3" t="n">
         <v>6058</v>
       </c>
     </row>
@@ -2486,28 +2498,28 @@
           <t>magnesium</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="3" t="n">
+      <c r="B62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="D62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="3" t="n">
+      <c r="D62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="2" t="n">
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="3" t="n">
         <v>43112</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="K62" s="3" t="n">
         <v>6058</v>
       </c>
     </row>
@@ -2517,34 +2529,34 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="C63" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="F63" s="3" t="n">
+      <c r="F63" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="G63" s="3" t="n">
+      <c r="G63" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="5" t="n">
         <v>82.8</v>
       </c>
-      <c r="I63" s="5" t="n">
+      <c r="I63" s="6" t="n">
         <v>0.1705899002702172</v>
       </c>
-      <c r="J63" s="2" t="n">
+      <c r="J63" s="3" t="n">
         <v>607190</v>
       </c>
-      <c r="K63" s="2" t="n">
+      <c r="K63" s="3" t="n">
         <v>20690</v>
       </c>
     </row>
@@ -2554,28 +2566,28 @@
           <t>antioxidants</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="C64" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="4" t="n">
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="5" t="n">
         <v>90.7</v>
       </c>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="2" t="n">
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="3" t="n">
         <v>50507</v>
       </c>
-      <c r="K64" s="2" t="n">
+      <c r="K64" s="3" t="n">
         <v>7155</v>
       </c>
     </row>
@@ -2585,28 +2597,28 @@
           <t>butyric_acid</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="3" t="n">
+      <c r="B65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="2" t="n">
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2614,28 +2626,28 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="4" t="n">
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="5" t="n">
         <v>44.6</v>
       </c>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="2" t="n">
+      <c r="I66" s="6" t="inlineStr"/>
+      <c r="J66" s="3" t="n">
         <v>200518</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="K66" s="3" t="n">
         <v>7678</v>
       </c>
     </row>
@@ -2645,28 +2657,28 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="3" t="n">
+      <c r="B67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="2" t="n">
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="3" t="n">
         <v>21533</v>
       </c>
-      <c r="K67" s="2" t="n">
+      <c r="K67" s="3" t="n">
         <v>291</v>
       </c>
     </row>
@@ -2676,34 +2688,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="C68" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="F68" s="4" t="n">
         <v>0.24</v>
       </c>
-      <c r="G68" s="3" t="n">
+      <c r="G68" s="4" t="n">
         <v>5.08</v>
       </c>
-      <c r="H68" s="4" t="n">
+      <c r="H68" s="5" t="n">
         <v>83.3</v>
       </c>
-      <c r="I68" s="5" t="n">
+      <c r="I68" s="6" t="n">
         <v>0.1158775811071888</v>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="3" t="n">
         <v>79458</v>
       </c>
-      <c r="K68" s="2" t="n">
+      <c r="K68" s="3" t="n">
         <v>7209</v>
       </c>
     </row>
@@ -2713,28 +2725,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="3" t="n">
+      <c r="B69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="2" t="n">
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="3" t="n">
         <v>47885</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="K69" s="3" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2744,34 +2756,34 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="F70" s="4" t="n">
         <v>0.13</v>
       </c>
-      <c r="G70" s="3" t="n">
+      <c r="G70" s="4" t="n">
         <v>9.68</v>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="5" t="n">
         <v>89.2</v>
       </c>
-      <c r="I70" s="5" t="n">
-        <v>0.001324630547994087</v>
-      </c>
-      <c r="J70" s="2" t="n">
+      <c r="I70" s="6" t="n">
+        <v>0.00132463054799409</v>
+      </c>
+      <c r="J70" s="3" t="n">
         <v>3207</v>
       </c>
-      <c r="K70" s="2" t="n">
+      <c r="K70" s="3" t="n">
         <v>1358</v>
       </c>
     </row>
@@ -2781,34 +2793,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C71" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="F71" s="3" t="n">
+      <c r="F71" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="G71" s="3" t="n">
+      <c r="G71" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="H71" s="5" t="n">
         <v>71.2</v>
       </c>
-      <c r="I71" s="5" t="n">
-        <v>0.002637956795546261</v>
-      </c>
-      <c r="J71" s="2" t="n">
+      <c r="I71" s="6" t="n">
+        <v>0.002637956795546257</v>
+      </c>
+      <c r="J71" s="3" t="n">
         <v>1091655</v>
       </c>
-      <c r="K71" s="2" t="n">
+      <c r="K71" s="3" t="n">
         <v>65703</v>
       </c>
     </row>
@@ -2818,34 +2830,34 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="C72" s="4" t="n">
         <v>1.14</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="F72" s="3" t="n">
+      <c r="F72" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="G72" s="3" t="n">
+      <c r="G72" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="H72" s="5" t="n">
         <v>11.1</v>
       </c>
-      <c r="I72" s="5" t="n">
-        <v>0.9371736085394766</v>
-      </c>
-      <c r="J72" s="2" t="n">
+      <c r="I72" s="6" t="n">
+        <v>0.9371736085394762</v>
+      </c>
+      <c r="J72" s="3" t="n">
         <v>348954</v>
       </c>
-      <c r="K72" s="2" t="n">
+      <c r="K72" s="3" t="n">
         <v>4443</v>
       </c>
     </row>
@@ -2855,34 +2867,34 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="4" t="n">
         <v>1.51</v>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F73" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="G73" s="3" t="n">
+      <c r="G73" s="4" t="n">
         <v>2.59</v>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="5" t="n">
         <v>71.2</v>
       </c>
-      <c r="I73" s="5" t="n">
-        <v>0.8512478924325507</v>
-      </c>
-      <c r="J73" s="2" t="n">
+      <c r="I73" s="6" t="n">
+        <v>0.8512478924325504</v>
+      </c>
+      <c r="J73" s="3" t="n">
         <v>94876</v>
       </c>
-      <c r="K73" s="2" t="n">
+      <c r="K73" s="3" t="n">
         <v>7312</v>
       </c>
     </row>
@@ -2892,34 +2904,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="C74" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="F74" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G74" s="3" t="n">
+      <c r="G74" s="4" t="n">
         <v>1.66</v>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="5" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="I74" s="5" t="n">
-        <v>0.00552361906352278</v>
-      </c>
-      <c r="J74" s="2" t="n">
+      <c r="I74" s="6" t="n">
+        <v>0.005523619063522757</v>
+      </c>
+      <c r="J74" s="3" t="n">
         <v>1934957</v>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2927,34 +2939,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C75" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="F75" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G75" s="3" t="n">
+      <c r="G75" s="4" t="n">
         <v>1.81</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="I75" s="5" t="n">
-        <v>0.007502544100791496</v>
-      </c>
-      <c r="J75" s="2" t="n">
+      <c r="I75" s="6" t="n">
+        <v>0.007502544100791495</v>
+      </c>
+      <c r="J75" s="3" t="n">
         <v>673771</v>
       </c>
-      <c r="K75" s="2" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2962,34 +2974,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C76" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="F76" s="3" t="n">
+      <c r="F76" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="G76" s="3" t="n">
+      <c r="G76" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="5" t="n">
         <v>82.7</v>
       </c>
-      <c r="I76" s="5" t="n">
-        <v>0.09941545468620654</v>
-      </c>
-      <c r="J76" s="2" t="n">
+      <c r="I76" s="6" t="n">
+        <v>0.09941545468620652</v>
+      </c>
+      <c r="J76" s="3" t="n">
         <v>739672</v>
       </c>
-      <c r="K76" s="2" t="n">
+      <c r="K76" s="3" t="n">
         <v>33998</v>
       </c>
     </row>
@@ -2999,34 +3011,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="G77" s="3" t="n">
+      <c r="G77" s="4" t="n">
         <v>1.72</v>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="5" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="I77" s="5" t="n">
-        <v>0.04484903666718717</v>
-      </c>
-      <c r="J77" s="2" t="n">
+      <c r="I77" s="6" t="n">
+        <v>0.04484903666718724</v>
+      </c>
+      <c r="J77" s="3" t="n">
         <v>770289</v>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3034,34 +3046,34 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C78" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="D78" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="3" t="n">
+      <c r="D78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="G78" s="3" t="n">
+      <c r="G78" s="4" t="n">
         <v>12.86</v>
       </c>
-      <c r="H78" s="4" t="n">
+      <c r="H78" s="5" t="n">
         <v>50.3</v>
       </c>
-      <c r="I78" s="5" t="n">
-        <v>0.2572200177327541</v>
-      </c>
-      <c r="J78" s="2" t="n">
+      <c r="I78" s="6" t="n">
+        <v>0.257220017732754</v>
+      </c>
+      <c r="J78" s="3" t="n">
         <v>201324</v>
       </c>
-      <c r="K78" s="2" t="n">
+      <c r="K78" s="3" t="n">
         <v>7680</v>
       </c>
     </row>
@@ -3071,34 +3083,34 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="G79" s="3" t="n">
+      <c r="G79" s="4" t="n">
         <v>2.01</v>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="5" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="I79" s="5" t="n">
+      <c r="I79" s="6" t="n">
         <v>0.02035566769413238</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J79" s="3" t="n">
         <v>255429</v>
       </c>
-      <c r="K79" s="2" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3106,34 +3118,34 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="C80" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="4" t="n">
         <v>1.62</v>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G80" s="3" t="n">
+      <c r="G80" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="H80" s="4" t="n">
+      <c r="H80" s="5" t="n">
         <v>88.7</v>
       </c>
-      <c r="I80" s="5" t="n">
-        <v>0.02622839085694529</v>
-      </c>
-      <c r="J80" s="2" t="n">
+      <c r="I80" s="6" t="n">
+        <v>0.02622839085694527</v>
+      </c>
+      <c r="J80" s="3" t="n">
         <v>556471</v>
       </c>
-      <c r="K80" s="2" t="n">
+      <c r="K80" s="3" t="n">
         <v>12655</v>
       </c>
     </row>
@@ -3143,28 +3155,28 @@
           <t>mineral_supplements</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="4" t="n">
         <v>2.26</v>
       </c>
-      <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr"/>
-      <c r="H81" s="4" t="n">
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr"/>
+      <c r="H81" s="5" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="2" t="n">
+      <c r="I81" s="6" t="inlineStr"/>
+      <c r="J81" s="3" t="n">
         <v>57251</v>
       </c>
-      <c r="K81" s="2" t="n">
+      <c r="K81" s="3" t="n">
         <v>1958</v>
       </c>
     </row>
@@ -3174,34 +3186,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="C82" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="4" t="n">
         <v>2.01</v>
       </c>
-      <c r="F82" s="3" t="n">
+      <c r="F82" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="G82" s="3" t="n">
+      <c r="G82" s="4" t="n">
         <v>159.52</v>
       </c>
-      <c r="H82" s="4" t="n">
+      <c r="H82" s="5" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="I82" s="5" t="n">
-        <v>0.6751776574754228</v>
-      </c>
-      <c r="J82" s="2" t="n">
+      <c r="I82" s="6" t="n">
+        <v>0.6751776574754227</v>
+      </c>
+      <c r="J82" s="3" t="n">
         <v>247791</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="K82" s="3" t="n">
         <v>29373</v>
       </c>
     </row>
@@ -3211,28 +3223,28 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" s="3" t="n">
+      <c r="B83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="4" t="n">
         <v>1.64</v>
       </c>
-      <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="2" t="n">
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr"/>
+      <c r="J83" s="3" t="n">
         <v>2611</v>
       </c>
-      <c r="K83" s="2" t="n">
+      <c r="K83" s="3" t="n">
         <v>1499</v>
       </c>
     </row>
@@ -3242,28 +3254,28 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C84" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D84" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="3" t="n">
+      <c r="D84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
-      <c r="H84" s="4" t="n">
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="5" t="n">
         <v>57.1</v>
       </c>
-      <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="2" t="n">
+      <c r="I84" s="6" t="inlineStr"/>
+      <c r="J84" s="3" t="n">
         <v>44462</v>
       </c>
-      <c r="K84" s="2" t="n">
+      <c r="K84" s="3" t="n">
         <v>1702</v>
       </c>
     </row>
@@ -3273,34 +3285,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="C85" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="4" t="n">
         <v>2.45</v>
       </c>
-      <c r="F85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="3" t="n">
+      <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="n">
         <v>664.3099999999999</v>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="I85" s="5" t="n">
-        <v>0.1814798483236069</v>
-      </c>
-      <c r="J85" s="2" t="n">
+      <c r="I85" s="6" t="n">
+        <v>0.1814798483236068</v>
+      </c>
+      <c r="J85" s="3" t="n">
         <v>3460</v>
       </c>
-      <c r="K85" s="2" t="n">
+      <c r="K85" s="3" t="n">
         <v>339</v>
       </c>
     </row>
@@ -3310,28 +3322,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="3" t="n">
+      <c r="B86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="E86" s="3" t="n">
+      <c r="E86" s="4" t="n">
         <v>2.19</v>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
-      <c r="H86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="2" t="n">
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="3" t="n">
         <v>58279</v>
       </c>
-      <c r="K86" s="2" t="n">
+      <c r="K86" s="3" t="n">
         <v>642</v>
       </c>
     </row>
@@ -3341,28 +3353,28 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="C87" s="4" t="n">
         <v>1.47</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E87" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="F87" s="3" t="inlineStr"/>
-      <c r="G87" s="3" t="inlineStr"/>
-      <c r="H87" s="4" t="n">
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="2" t="n">
+      <c r="I87" s="6" t="inlineStr"/>
+      <c r="J87" s="3" t="n">
         <v>719</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="K87" s="3" t="n">
         <v>245</v>
       </c>
     </row>
@@ -3372,34 +3384,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="C88" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="F88" s="3" t="n">
+      <c r="F88" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G88" s="3" t="n">
+      <c r="G88" s="4" t="n">
         <v>4.51</v>
       </c>
-      <c r="H88" s="4" t="n">
+      <c r="H88" s="5" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="I88" s="5" t="n">
-        <v>0.01959176169058002</v>
-      </c>
-      <c r="J88" s="2" t="n">
+      <c r="I88" s="6" t="n">
+        <v>0.01959176169058001</v>
+      </c>
+      <c r="J88" s="3" t="n">
         <v>974550</v>
       </c>
-      <c r="K88" s="2" t="n">
+      <c r="K88" s="3" t="n">
         <v>57630</v>
       </c>
     </row>
@@ -3409,28 +3421,28 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" s="3" t="n">
+      <c r="B89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="4" t="n">
         <v>2.97</v>
       </c>
-      <c r="E89" s="3" t="n">
+      <c r="E89" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="2" t="n">
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr"/>
+      <c r="J89" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="K89" s="2" t="n">
+      <c r="K89" s="3" t="n">
         <v>130</v>
       </c>
     </row>

--- a/summary/yes/exposures_meta_analysis_prostate_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_prostate_cancer_dietary.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,28 +514,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>102</v>
       </c>
     </row>
@@ -557,28 +545,28 @@
           <t>natto</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>140</v>
       </c>
     </row>
@@ -588,28 +576,28 @@
           <t>papaya</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
     </row>
@@ -619,28 +607,28 @@
           <t>early_time_restricted_eating</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>607</v>
       </c>
     </row>
@@ -650,34 +638,34 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.41</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="4" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="I6" s="6" t="n">
-        <v>0.1010785350953813</v>
-      </c>
-      <c r="J6" s="3" t="n">
+      <c r="I6" s="5" t="n">
+        <v>0.1010785350953814</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>85059</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>5399</v>
       </c>
     </row>
@@ -687,34 +675,34 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="3" t="n">
         <v>1.92</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="4" t="n">
         <v>72.7</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>0.1767576153047416</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="I7" s="5" t="n">
+        <v>0.1767576153047418</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>99090</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>1577</v>
       </c>
     </row>
@@ -724,34 +712,34 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="n">
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>206.11</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="5" t="n">
         <v>0.1151715356999109</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="2" t="n">
         <v>101084</v>
       </c>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -759,28 +747,28 @@
           <t>low_fat_diet</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="3" t="n">
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
         <v>1170</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>390</v>
       </c>
     </row>
@@ -790,28 +778,28 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="3" t="n">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>1623</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>677</v>
       </c>
     </row>
@@ -821,28 +809,28 @@
           <t>vitamin_k</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="3" t="n">
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -852,28 +840,28 @@
           <t>vitamin_k2</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -883,28 +871,28 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="3" t="n">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>971</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>433</v>
       </c>
     </row>
@@ -914,28 +902,28 @@
           <t>vegan_diet</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="3" t="n">
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
         <v>26346</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>1079</v>
       </c>
     </row>
@@ -945,34 +933,34 @@
           <t>garlic</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>265.07</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="5" t="n">
         <v>0.2044018200861738</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="2" t="n">
         <v>36604</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -982,28 +970,28 @@
           <t>vegetarian_diet</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="4" t="n">
+      <c r="B16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="3" t="n">
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="2" t="n">
         <v>217937</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>9501</v>
       </c>
     </row>
@@ -1013,34 +1001,34 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="4" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="I17" s="6" t="n">
-        <v>2.045420729252859e-05</v>
-      </c>
-      <c r="J17" s="3" t="n">
+      <c r="I17" s="5" t="n">
+        <v>2.045420729252854e-05</v>
+      </c>
+      <c r="J17" s="2" t="n">
         <v>1057923</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>67108</v>
       </c>
     </row>
@@ -1050,34 +1038,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="4" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>0.0499620846835085</v>
-      </c>
-      <c r="J18" s="3" t="n">
+      <c r="I18" s="5" t="n">
+        <v>0.04996208468350868</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>314398</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>15389</v>
       </c>
     </row>
@@ -1087,28 +1075,28 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="n">
+      <c r="B19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>652</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>244</v>
       </c>
     </row>
@@ -1118,28 +1106,28 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="n">
+      <c r="B20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="3" t="n">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
         <v>656</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1149,34 +1137,34 @@
           <t>genistein</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.37</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.63</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>6253.84</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <v>0.05600670850526827</v>
-      </c>
-      <c r="J21" s="3" t="n">
+      <c r="I21" s="5" t="n">
+        <v>0.05600670850526847</v>
+      </c>
+      <c r="J21" s="2" t="n">
         <v>70911</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>727</v>
       </c>
     </row>
@@ -1186,28 +1174,28 @@
           <t>iodine</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="n">
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="3" t="n">
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
         <v>656</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1217,34 +1205,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="3" t="n">
         <v>0.41</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="4" t="n">
         <v>64.5</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <v>0.04074875994005017</v>
-      </c>
-      <c r="J23" s="3" t="n">
+      <c r="I23" s="5" t="n">
+        <v>0.04074875994005019</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>94949</v>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1252,28 +1240,28 @@
           <t>time_restricted_eating</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="n">
+      <c r="B24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="3" t="n">
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>607</v>
       </c>
     </row>
@@ -1283,28 +1271,28 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4" t="n">
+      <c r="B25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="3" t="n">
+      <c r="E25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="2" t="n">
         <v>2745</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1314,28 +1302,28 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="n">
+      <c r="B26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
         <v>2745</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1345,28 +1333,28 @@
           <t>mushrooms</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>36499</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -1376,34 +1364,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="4" t="n">
         <v>80.7</v>
       </c>
-      <c r="I28" s="6" t="n">
-        <v>0.8930041904516861</v>
-      </c>
-      <c r="J28" s="3" t="n">
+      <c r="I28" s="5" t="n">
+        <v>0.8930041904516864</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>68446</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>7637</v>
       </c>
     </row>
@@ -1413,34 +1401,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="4" t="n">
         <v>69.5</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <v>0.0749554992913304</v>
-      </c>
-      <c r="J29" s="3" t="n">
+      <c r="I29" s="5" t="n">
+        <v>0.07495549929133036</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>282888</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>22602</v>
       </c>
     </row>
@@ -1450,34 +1438,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="4" t="n">
         <v>55.4</v>
       </c>
-      <c r="I30" s="6" t="n">
-        <v>0.7901812753667304</v>
-      </c>
-      <c r="J30" s="3" t="n">
+      <c r="I30" s="5" t="n">
+        <v>0.7901812753667296</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <v>131386</v>
       </c>
-      <c r="K30" s="3" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1485,34 +1473,34 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" s="4" t="n">
         <v>62.4</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>0.006170430008920973</v>
-      </c>
-      <c r="J31" s="3" t="n">
+      <c r="I31" s="5" t="n">
+        <v>0.00617043000892098</v>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>1155076</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>79072</v>
       </c>
     </row>
@@ -1522,34 +1510,34 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>0.188399637329524</v>
-      </c>
-      <c r="J32" s="3" t="n">
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.1883996373295245</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>80888</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>10851</v>
       </c>
     </row>
@@ -1559,34 +1547,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0.2443574036478493</v>
-      </c>
-      <c r="J33" s="3" t="n">
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.2443574036478494</v>
+      </c>
+      <c r="J33" s="2" t="n">
         <v>70879</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>7656</v>
       </c>
     </row>
@@ -1596,28 +1584,28 @@
           <t>plant_based_diet</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="5" t="n">
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="3" t="n">
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="2" t="n">
         <v>211318</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>24516</v>
       </c>
     </row>
@@ -1627,28 +1615,28 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4" t="n">
+      <c r="B35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="3" t="n">
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
         <v>46667</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -1658,28 +1646,28 @@
           <t>ginseng</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4" t="n">
+      <c r="B36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="3" t="n">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1689,34 +1677,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4" t="n">
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="4" t="n">
         <v>42.9</v>
       </c>
-      <c r="I37" s="6" t="n">
-        <v>0.07744276379719461</v>
-      </c>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="n">
+        <v>0.0774427637971946</v>
+      </c>
+      <c r="J37" s="2" t="n">
         <v>972077</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>64899</v>
       </c>
     </row>
@@ -1726,28 +1714,28 @@
           <t>dash_diet</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="n">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="n">
         <v>73.90000000000001</v>
       </c>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
         <v>152714</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1755,28 +1743,28 @@
           <t>ginkgo_biloba</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="n">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>38308</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>1665</v>
       </c>
     </row>
@@ -1786,28 +1774,28 @@
           <t>coenzyme_q10</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="n">
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="3" t="n">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1817,28 +1805,28 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="5" t="n">
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="3" t="n">
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
         <v>430507</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>7761</v>
       </c>
     </row>
@@ -1848,34 +1836,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="4" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="I42" s="6" t="n">
-        <v>0.116278835132563</v>
-      </c>
-      <c r="J42" s="3" t="n">
+      <c r="I42" s="5" t="n">
+        <v>0.1162788351325633</v>
+      </c>
+      <c r="J42" s="2" t="n">
         <v>270107</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>13301</v>
       </c>
     </row>
@@ -1885,28 +1873,28 @@
           <t>fish_oil</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4" t="n">
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="3" t="n">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1916,28 +1904,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="4" t="n">
+      <c r="B44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
         <v>150671</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>14238</v>
       </c>
     </row>
@@ -1947,28 +1935,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="n">
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="3" t="n">
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="2" t="n">
         <v>159482</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>17349</v>
       </c>
     </row>
@@ -1978,28 +1966,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="3" t="n">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>109557</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -2009,34 +1997,34 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="H47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="6" t="n">
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="n">
         <v>0.8121269612161565</v>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="J47" s="2" t="n">
         <v>900752</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>53381</v>
       </c>
     </row>
@@ -2046,28 +2034,28 @@
           <t>docosapentaenoic_acid_omega_3</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="4" t="n">
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="3" t="n">
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="2" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2077,28 +2065,28 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="4" t="n">
+      <c r="C49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="5" t="n">
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="4" t="n">
         <v>69.5</v>
       </c>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="3" t="n">
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>106146</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="2" t="n">
         <v>7476</v>
       </c>
     </row>
@@ -2108,28 +2096,28 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="4" t="n">
+      <c r="B50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr"/>
-      <c r="J50" s="3" t="n">
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" s="2" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2139,28 +2127,28 @@
           <t>gondoic_acid</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="4" t="n">
+      <c r="B51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr"/>
-      <c r="J51" s="3" t="n">
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" s="2" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2170,28 +2158,28 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="4" t="n">
+      <c r="B52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="3" t="n">
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="2" t="n">
         <v>47896</v>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" s="2" t="n">
         <v>695</v>
       </c>
     </row>
@@ -2201,28 +2189,28 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="4" t="n">
+      <c r="B53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="3" t="n">
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="2" t="n">
         <v>6528</v>
       </c>
-      <c r="K53" s="3" t="n">
+      <c r="K53" s="2" t="n">
         <v>811</v>
       </c>
     </row>
@@ -2232,34 +2220,34 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="C54" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="H54" s="4" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="I54" s="6" t="n">
-        <v>0.477456001463626</v>
-      </c>
-      <c r="J54" s="3" t="n">
+      <c r="I54" s="5" t="n">
+        <v>0.4774560014636261</v>
+      </c>
+      <c r="J54" s="2" t="n">
         <v>183783</v>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" s="2" t="n">
         <v>11462</v>
       </c>
     </row>
@@ -2269,34 +2257,34 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C55" s="4" t="n">
+      <c r="C55" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H55" s="4" t="n">
         <v>43.6</v>
       </c>
-      <c r="I55" s="6" t="n">
-        <v>0.08106606109529807</v>
-      </c>
-      <c r="J55" s="3" t="n">
+      <c r="I55" s="5" t="n">
+        <v>0.08106606109529818</v>
+      </c>
+      <c r="J55" s="2" t="n">
         <v>235441</v>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="K55" s="2" t="n">
         <v>18652</v>
       </c>
     </row>
@@ -2306,34 +2294,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="H56" s="5" t="n">
+      <c r="H56" s="4" t="n">
         <v>38.1</v>
       </c>
-      <c r="I56" s="6" t="n">
-        <v>0.4142673366090839</v>
-      </c>
-      <c r="J56" s="3" t="n">
+      <c r="I56" s="5" t="n">
+        <v>0.4142673366090832</v>
+      </c>
+      <c r="J56" s="2" t="n">
         <v>248736</v>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="K56" s="2" t="n">
         <v>13760</v>
       </c>
     </row>
@@ -2343,28 +2331,28 @@
           <t>vitamin_k1</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="4" t="n">
+      <c r="B57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr"/>
-      <c r="J57" s="3" t="n">
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="K57" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2374,28 +2362,28 @@
           <t>saw_palmetto</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="4" t="n">
+      <c r="B58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr"/>
-      <c r="J58" s="3" t="n">
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2405,28 +2393,28 @@
           <t>glucosamine</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="4" t="n">
+      <c r="B59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="3" t="n">
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K59" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2436,28 +2424,28 @@
           <t>chondroitin</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="4" t="n">
+      <c r="B60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr"/>
-      <c r="J60" s="3" t="n">
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2467,28 +2455,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="n">
+      <c r="B61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="D61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="4" t="n">
+      <c r="D61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="3" t="n">
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="2" t="n">
         <v>43112</v>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="K61" s="2" t="n">
         <v>6058</v>
       </c>
     </row>
@@ -2498,28 +2486,28 @@
           <t>magnesium</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="4" t="n">
+      <c r="B62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="D62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="4" t="n">
+      <c r="D62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr"/>
-      <c r="J62" s="3" t="n">
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="2" t="n">
         <v>43112</v>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="K62" s="2" t="n">
         <v>6058</v>
       </c>
     </row>
@@ -2529,34 +2517,34 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
+      <c r="B63" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C63" s="4" t="n">
+      <c r="C63" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="F63" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="H63" s="5" t="n">
+      <c r="H63" s="4" t="n">
         <v>82.8</v>
       </c>
-      <c r="I63" s="6" t="n">
+      <c r="I63" s="5" t="n">
         <v>0.1705899002702172</v>
       </c>
-      <c r="J63" s="3" t="n">
+      <c r="J63" s="2" t="n">
         <v>607190</v>
       </c>
-      <c r="K63" s="3" t="n">
+      <c r="K63" s="2" t="n">
         <v>20690</v>
       </c>
     </row>
@@ -2566,28 +2554,28 @@
           <t>antioxidants</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
+      <c r="B64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="C64" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="5" t="n">
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="4" t="n">
         <v>90.7</v>
       </c>
-      <c r="I64" s="6" t="inlineStr"/>
-      <c r="J64" s="3" t="n">
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="2" t="n">
         <v>50507</v>
       </c>
-      <c r="K64" s="3" t="n">
+      <c r="K64" s="2" t="n">
         <v>7155</v>
       </c>
     </row>
@@ -2597,28 +2585,28 @@
           <t>butyric_acid</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="4" t="n">
+      <c r="B65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
-      <c r="H65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr"/>
-      <c r="J65" s="3" t="n">
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K65" s="3" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2626,28 +2614,28 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="5" t="n">
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="4" t="n">
         <v>44.6</v>
       </c>
-      <c r="I66" s="6" t="inlineStr"/>
-      <c r="J66" s="3" t="n">
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="2" t="n">
         <v>200518</v>
       </c>
-      <c r="K66" s="3" t="n">
+      <c r="K66" s="2" t="n">
         <v>7678</v>
       </c>
     </row>
@@ -2657,28 +2645,28 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="4" t="n">
+      <c r="B67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="3" t="n">
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="2" t="n">
         <v>21533</v>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="K67" s="2" t="n">
         <v>291</v>
       </c>
     </row>
@@ -2688,34 +2676,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="C68" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="3" t="n">
         <v>1.26</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="3" t="n">
         <v>5.08</v>
       </c>
-      <c r="H68" s="5" t="n">
+      <c r="H68" s="4" t="n">
         <v>83.3</v>
       </c>
-      <c r="I68" s="6" t="n">
+      <c r="I68" s="5" t="n">
         <v>0.1158775811071888</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="J68" s="2" t="n">
         <v>79458</v>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="K68" s="2" t="n">
         <v>7209</v>
       </c>
     </row>
@@ -2725,28 +2713,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="4" t="n">
+      <c r="B69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="3" t="n">
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="2" t="n">
         <v>47885</v>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="K69" s="2" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2756,34 +2744,34 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C70" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="3" t="n">
         <v>1.99</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="3" t="n">
         <v>9.68</v>
       </c>
-      <c r="H70" s="5" t="n">
+      <c r="H70" s="4" t="n">
         <v>89.2</v>
       </c>
-      <c r="I70" s="6" t="n">
-        <v>0.00132463054799409</v>
-      </c>
-      <c r="J70" s="3" t="n">
+      <c r="I70" s="5" t="n">
+        <v>0.001324630547994084</v>
+      </c>
+      <c r="J70" s="2" t="n">
         <v>3207</v>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="K70" s="2" t="n">
         <v>1358</v>
       </c>
     </row>
@@ -2793,34 +2781,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n">
+      <c r="B71" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C71" s="4" t="n">
+      <c r="C71" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="H71" s="5" t="n">
+      <c r="H71" s="4" t="n">
         <v>71.2</v>
       </c>
-      <c r="I71" s="6" t="n">
-        <v>0.002637956795546257</v>
-      </c>
-      <c r="J71" s="3" t="n">
+      <c r="I71" s="5" t="n">
+        <v>0.002637956795546261</v>
+      </c>
+      <c r="J71" s="2" t="n">
         <v>1091655</v>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" s="2" t="n">
         <v>65703</v>
       </c>
     </row>
@@ -2830,34 +2818,34 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n">
+      <c r="B72" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C72" s="4" t="n">
+      <c r="C72" s="3" t="n">
         <v>1.14</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="3" t="n">
         <v>1.71</v>
       </c>
-      <c r="H72" s="5" t="n">
+      <c r="H72" s="4" t="n">
         <v>11.1</v>
       </c>
-      <c r="I72" s="6" t="n">
-        <v>0.9371736085394762</v>
-      </c>
-      <c r="J72" s="3" t="n">
+      <c r="I72" s="5" t="n">
+        <v>0.9371736085394766</v>
+      </c>
+      <c r="J72" s="2" t="n">
         <v>348954</v>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="K72" s="2" t="n">
         <v>4443</v>
       </c>
     </row>
@@ -2867,34 +2855,34 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B73" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="C73" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="3" t="n">
         <v>2.59</v>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="4" t="n">
         <v>71.2</v>
       </c>
-      <c r="I73" s="6" t="n">
-        <v>0.8512478924325504</v>
-      </c>
-      <c r="J73" s="3" t="n">
+      <c r="I73" s="5" t="n">
+        <v>0.8512478924325507</v>
+      </c>
+      <c r="J73" s="2" t="n">
         <v>94876</v>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" s="2" t="n">
         <v>7312</v>
       </c>
     </row>
@@ -2904,34 +2892,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B74" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="C74" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="H74" s="5" t="n">
+      <c r="H74" s="4" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="I74" s="6" t="n">
-        <v>0.005523619063522757</v>
-      </c>
-      <c r="J74" s="3" t="n">
+      <c r="I74" s="5" t="n">
+        <v>0.005523619063522766</v>
+      </c>
+      <c r="J74" s="2" t="n">
         <v>1934957</v>
       </c>
-      <c r="K74" s="3" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2939,34 +2927,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C75" s="4" t="n">
+      <c r="C75" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="3" t="n">
         <v>1.81</v>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="I75" s="6" t="n">
-        <v>0.007502544100791495</v>
-      </c>
-      <c r="J75" s="3" t="n">
+      <c r="I75" s="5" t="n">
+        <v>0.007502544100791496</v>
+      </c>
+      <c r="J75" s="2" t="n">
         <v>673771</v>
       </c>
-      <c r="K75" s="3" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2974,34 +2962,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B76" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C76" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="3" t="n">
         <v>1.79</v>
       </c>
-      <c r="H76" s="5" t="n">
+      <c r="H76" s="4" t="n">
         <v>82.7</v>
       </c>
-      <c r="I76" s="6" t="n">
-        <v>0.09941545468620652</v>
-      </c>
-      <c r="J76" s="3" t="n">
+      <c r="I76" s="5" t="n">
+        <v>0.09941545468620654</v>
+      </c>
+      <c r="J76" s="2" t="n">
         <v>739672</v>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="K76" s="2" t="n">
         <v>33998</v>
       </c>
     </row>
@@ -3011,34 +2999,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C77" s="4" t="n">
+      <c r="C77" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="3" t="n">
         <v>1.72</v>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="4" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="I77" s="6" t="n">
-        <v>0.04484903666718724</v>
-      </c>
-      <c r="J77" s="3" t="n">
+      <c r="I77" s="5" t="n">
+        <v>0.04484903666718717</v>
+      </c>
+      <c r="J77" s="2" t="n">
         <v>770289</v>
       </c>
-      <c r="K77" s="3" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3046,34 +3034,34 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="C78" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="D78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="4" t="n">
+      <c r="D78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="3" t="n">
         <v>12.86</v>
       </c>
-      <c r="H78" s="5" t="n">
+      <c r="H78" s="4" t="n">
         <v>50.3</v>
       </c>
-      <c r="I78" s="6" t="n">
-        <v>0.257220017732754</v>
-      </c>
-      <c r="J78" s="3" t="n">
+      <c r="I78" s="5" t="n">
+        <v>0.2572200177327541</v>
+      </c>
+      <c r="J78" s="2" t="n">
         <v>201324</v>
       </c>
-      <c r="K78" s="3" t="n">
+      <c r="K78" s="2" t="n">
         <v>7680</v>
       </c>
     </row>
@@ -3083,34 +3071,34 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C79" s="4" t="n">
+      <c r="C79" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="4" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="I79" s="6" t="n">
+      <c r="I79" s="5" t="n">
         <v>0.02035566769413238</v>
       </c>
-      <c r="J79" s="3" t="n">
+      <c r="J79" s="2" t="n">
         <v>255429</v>
       </c>
-      <c r="K79" s="3" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3118,34 +3106,34 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C80" s="4" t="n">
+      <c r="C80" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="H80" s="5" t="n">
+      <c r="H80" s="4" t="n">
         <v>88.7</v>
       </c>
-      <c r="I80" s="6" t="n">
-        <v>0.02622839085694527</v>
-      </c>
-      <c r="J80" s="3" t="n">
+      <c r="I80" s="5" t="n">
+        <v>0.02622839085694529</v>
+      </c>
+      <c r="J80" s="2" t="n">
         <v>556471</v>
       </c>
-      <c r="K80" s="3" t="n">
+      <c r="K80" s="2" t="n">
         <v>12655</v>
       </c>
     </row>
@@ -3155,28 +3143,28 @@
           <t>mineral_supplements</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C81" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="3" t="n">
         <v>2.26</v>
       </c>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr"/>
-      <c r="H81" s="5" t="n">
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="4" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="I81" s="6" t="inlineStr"/>
-      <c r="J81" s="3" t="n">
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="2" t="n">
         <v>57251</v>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="K81" s="2" t="n">
         <v>1958</v>
       </c>
     </row>
@@ -3186,34 +3174,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B82" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C82" s="4" t="n">
+      <c r="C82" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="3" t="n">
         <v>159.52</v>
       </c>
-      <c r="H82" s="5" t="n">
+      <c r="H82" s="4" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="I82" s="6" t="n">
-        <v>0.6751776574754227</v>
-      </c>
-      <c r="J82" s="3" t="n">
+      <c r="I82" s="5" t="n">
+        <v>0.6751776574754228</v>
+      </c>
+      <c r="J82" s="2" t="n">
         <v>247791</v>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="K82" s="2" t="n">
         <v>29373</v>
       </c>
     </row>
@@ -3223,28 +3211,28 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" s="4" t="n">
+      <c r="B83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr"/>
-      <c r="H83" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr"/>
-      <c r="J83" s="3" t="n">
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="2" t="n">
         <v>2611</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="K83" s="2" t="n">
         <v>1499</v>
       </c>
     </row>
@@ -3254,28 +3242,28 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="4" t="n">
+      <c r="D84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="5" t="n">
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="I84" s="6" t="inlineStr"/>
-      <c r="J84" s="3" t="n">
+      <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="2" t="n">
         <v>44462</v>
       </c>
-      <c r="K84" s="3" t="n">
+      <c r="K84" s="2" t="n">
         <v>1702</v>
       </c>
     </row>
@@ -3285,34 +3273,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B85" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C85" s="4" t="n">
+      <c r="C85" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="F85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4" t="n">
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
         <v>664.3099999999999</v>
       </c>
-      <c r="H85" s="5" t="n">
+      <c r="H85" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="I85" s="6" t="n">
-        <v>0.1814798483236068</v>
-      </c>
-      <c r="J85" s="3" t="n">
+      <c r="I85" s="5" t="n">
+        <v>0.1814798483236069</v>
+      </c>
+      <c r="J85" s="2" t="n">
         <v>3460</v>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="K85" s="2" t="n">
         <v>339</v>
       </c>
     </row>
@@ -3322,28 +3310,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="4" t="n">
+      <c r="B86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr"/>
-      <c r="J86" s="3" t="n">
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
         <v>58279</v>
       </c>
-      <c r="K86" s="3" t="n">
+      <c r="K86" s="2" t="n">
         <v>642</v>
       </c>
     </row>
@@ -3353,28 +3341,28 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
+      <c r="B87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C87" s="4" t="n">
+      <c r="C87" s="3" t="n">
         <v>1.47</v>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="D87" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr"/>
-      <c r="H87" s="5" t="n">
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr"/>
+      <c r="H87" s="4" t="n">
         <v>24.7</v>
       </c>
-      <c r="I87" s="6" t="inlineStr"/>
-      <c r="J87" s="3" t="n">
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="2" t="n">
         <v>719</v>
       </c>
-      <c r="K87" s="3" t="n">
+      <c r="K87" s="2" t="n">
         <v>245</v>
       </c>
     </row>
@@ -3384,34 +3372,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B88" s="3" t="n">
+      <c r="B88" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C88" s="4" t="n">
+      <c r="C88" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="3" t="n">
         <v>4.51</v>
       </c>
-      <c r="H88" s="5" t="n">
+      <c r="H88" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="I88" s="6" t="n">
-        <v>0.01959176169058001</v>
-      </c>
-      <c r="J88" s="3" t="n">
+      <c r="I88" s="5" t="n">
+        <v>0.01959176169058002</v>
+      </c>
+      <c r="J88" s="2" t="n">
         <v>974550</v>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="K88" s="2" t="n">
         <v>57630</v>
       </c>
     </row>
@@ -3421,28 +3409,28 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" s="4" t="n">
+      <c r="B89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="3" t="n">
         <v>4.58</v>
       </c>
-      <c r="D89" s="4" t="n">
+      <c r="D89" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="3" t="n">
         <v>5.94</v>
       </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr"/>
-      <c r="H89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr"/>
-      <c r="J89" s="3" t="n">
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="K89" s="2" t="n">
         <v>130</v>
       </c>
     </row>
